--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שחר אדמוני - כוכבים</v>
+        <v>שוקי סלומון &amp; שימי יונייב &amp; אייל טויטו - פורים פארטי 2 2026</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409835&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409850&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שחר אדמוני - כוכבים</v>
+        <v>שוקי סלומון &amp; שימי יונייב &amp; אייל טויטו - פורים פארטי 2 2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שולי בן - שיר עצוב</v>
+        <v>נתנאל - עושה שלום</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409834&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409849&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שולי בן - שיר עצוב</v>
+        <v>נתנאל - עושה שלום</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נוי מיהלי - כולם ישנים</v>
+        <v>שירן מור - מחרוזת שמחה באמונה 2026</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409833&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409848&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נוי מיהלי - כולם ישנים</v>
+        <v>שירן מור - מחרוזת שמחה באמונה 2026</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מקהלת משאלות - יתגשמו משאלות</v>
+        <v>רועי סנדלר - לכה דודי</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409832&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409847&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>מקהלת משאלות - יתגשמו משאלות</v>
+        <v>רועי סנדלר - לכה דודי</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>מני ממטרה &amp; דנה בנדנה - מסיבת פורים מטורפת 2026</v>
+        <v>ראובן המלאך - ילדים בודדים קאבר</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409831&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409846&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>מני ממטרה &amp; דנה בנדנה - מסיבת פורים מטורפת 2026</v>
+        <v>ראובן המלאך - ילדים בודדים קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>מוטי עויזר - מחרוזת פורים 2026</v>
+        <v>קלימה - אבא תן לי סימן</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409830&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409845&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>מוטי עויזר - מחרוזת פורים 2026</v>
+        <v>קלימה - אבא תן לי סימן</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ישי שין - חידושים</v>
+        <v>פנינה רוזנבלום &amp; אורן כהן - שאגת הארי</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409829&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409844&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>ישי שין - חידושים</v>
+        <v>פנינה רוזנבלום &amp; אורן כהן - שאגת הארי</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>יהנותן לוי - להעריך</v>
+        <v>נתלי - השטן לובשת פראדה</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409828&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409843&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>יהנותן לוי - להעריך</v>
+        <v>נתלי - השטן לובשת פראדה</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>חיים באינסאי - מיאמור</v>
+        <v>ירדן אזולאי - סגרת לי את הדלת</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409827&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409842&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>חיים באינסאי - מיאמור</v>
+        <v>ירדן אזולאי - סגרת לי את הדלת</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אורי דהן - מכתבים שרופים</v>
+        <v>יוסף מויאל - שאגת הארי</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409826&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409841&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -811,12 +811,202 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אורי דהן - מכתבים שרופים</v>
+        <v>יוסף מויאל - שאגת הארי</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>יובל קונסטנטיני - לא שלך</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-03-02</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409840&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>יובל קונסטנטיני - לא שלך</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>יגל יובל שרעבי - נוביה</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-03-02</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409839&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>יגל יובל שרעבי - נוביה</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>יגל יובל שרעבי - מכה על חטא</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-03-02</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409838&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>יגל יובל שרעבי - מכה על חטא</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>אליה נרקיס - מים מתוקים</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-03-02</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409837&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>אליה נרקיס - מים מתוקים</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>אליה דרעי - יש אחד</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-03-02</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409836&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>אליה דרעי - יש אחד</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L16"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שוקי סלומון &amp; שימי יונייב &amp; אייל טויטו - פורים פארטי 2 2026</v>
+        <v>תהילה זיאמר - הכל מסיבה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-04</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409850&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409868&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שוקי סלומון &amp; שימי יונייב &amp; אייל טויטו - פורים פארטי 2 2026</v>
+        <v>תהילה זיאמר - הכל מסיבה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נתנאל - עושה שלום</v>
+        <v>שגב בן נעים - השמש איחרה</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-04</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409849&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409867&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נתנאל - עושה שלום</v>
+        <v>שגב בן נעים - השמש איחרה</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שירן מור - מחרוזת שמחה באמונה 2026</v>
+        <v>נתנאל אברהם - מחרוזת כורדית 2026</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-04</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409848&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409866&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שירן מור - מחרוזת שמחה באמונה 2026</v>
+        <v>נתנאל אברהם - מחרוזת כורדית 2026</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>רועי סנדלר - לכה דודי</v>
+        <v>משה פרץ - יש על מי לסמוך</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-04</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409847&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409865&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>רועי סנדלר - לכה דודי</v>
+        <v>משה פרץ - יש על מי לסמוך</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ראובן המלאך - ילדים בודדים קאבר</v>
+        <v>טלי רבקה סימן טוב - הסוד</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-04</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409846&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409864&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>ראובן המלאך - ילדים בודדים קאבר</v>
+        <v>טלי רבקה סימן טוב - הסוד</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>קלימה - אבא תן לי סימן</v>
+        <v>הירושלמים - עוד אתה איתי</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-04</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409845&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409863&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>קלימה - אבא תן לי סימן</v>
+        <v>הירושלמים - עוד אתה איתי</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>פנינה רוזנבלום &amp; אורן כהן - שאגת הארי</v>
+        <v>דודו קדוש - מחרוזת בא לשכונה בחור חדש 2026</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-04</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409844&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409862&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>פנינה רוזנבלום &amp; אורן כהן - שאגת הארי</v>
+        <v>דודו קדוש - מחרוזת בא לשכונה בחור חדש 2026</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>נתלי - השטן לובשת פראדה</v>
+        <v>אורן כדורי - את אמיתית</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-04</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409843&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409861&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>נתלי - השטן לובשת פראדה</v>
+        <v>אורן כדורי - את אמיתית</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ירדן אזולאי - סגרת לי את הדלת</v>
+        <v>אור עמרמי ברוקמן - תמיד חוזר למנגינה</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-04</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409842&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409860&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>ירדן אזולאי - סגרת לי את הדלת</v>
+        <v>אור עמרמי ברוקמן - תמיד חוזר למנגינה</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>יוסף מויאל - שאגת הארי</v>
+        <v>אדל חן - קומי אורי</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-04</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409841&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409859&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -811,202 +811,12 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>יוסף מויאל - שאגת הארי</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>יובל קונסטנטיני - לא שלך</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-03-02</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409840&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>יובל קונסטנטיני - לא שלך</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>יגל יובל שרעבי - נוביה</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-03-02</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409839&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>יגל יובל שרעבי - נוביה</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>יגל יובל שרעבי - מכה על חטא</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-03-02</v>
-      </c>
-      <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409838&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>יגל יובל שרעבי - מכה על חטא</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>אליה נרקיס - מים מתוקים</v>
-      </c>
-      <c r="B15" t="str">
-        <v>2026-03-02</v>
-      </c>
-      <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409837&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
-      </c>
-      <c r="D15" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v>אליה נרקיס - מים מתוקים</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>אליה דרעי - יש אחד</v>
-      </c>
-      <c r="B16" t="str">
-        <v>2026-03-02</v>
-      </c>
-      <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409836&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
-      </c>
-      <c r="D16" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J16" t="str">
-        <v/>
-      </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-      <c r="L16" t="str">
-        <v>אליה דרעי - יש אחד</v>
+        <v>אדל חן - קומי אורי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תהילה זיאמר - הכל מסיבה</v>
+        <v>פרחי ירושלים &amp; עמירן דביר - ביי ביי חמינאי</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409868&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409887&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תהילה זיאמר - הכל מסיבה</v>
+        <v>פרחי ירושלים &amp; עמירן דביר - ביי ביי חמינאי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שגב בן נעים - השמש איחרה</v>
+        <v>אלחנן משמרתי - על משמרתי</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409867&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409886&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שגב בן נעים - השמש איחרה</v>
+        <v>אלחנן משמרתי - על משמרתי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נתנאל אברהם - מחרוזת כורדית 2026</v>
+        <v>שרוליק מנדלסון &amp; יענקי היל - שחרר לי את כל החסמים</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409866&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409885&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נתנאל אברהם - מחרוזת כורדית 2026</v>
+        <v>שרוליק מנדלסון &amp; יענקי היל - שחרר לי את כל החסמים</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>משה פרץ - יש על מי לסמוך</v>
+        <v>שנאל אלקיים - אל תבוא ואל תגיד לי</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409865&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409884&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>משה פרץ - יש על מי לסמוך</v>
+        <v>שנאל אלקיים - אל תבוא ואל תגיד לי</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>טלי רבקה סימן טוב - הסוד</v>
+        <v>שי לסרי - לא כמו פעם קאבר</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409864&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409883&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>טלי רבקה סימן טוב - הסוד</v>
+        <v>שי לסרי - לא כמו פעם קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>הירושלמים - עוד אתה איתי</v>
+        <v>פרחי ירושלים - אהבת השם</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409863&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409882&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>הירושלמים - עוד אתה איתי</v>
+        <v>פרחי ירושלים - אהבת השם</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>דודו קדוש - מחרוזת בא לשכונה בחור חדש 2026</v>
+        <v>עמי כהן &amp; גדולי הזמר - מחרוזת פורים עמישתה 2026</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409862&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409881&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>דודו קדוש - מחרוזת בא לשכונה בחור חדש 2026</v>
+        <v>עמי כהן &amp; גדולי הזמר - מחרוזת פורים עמישתה 2026</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אורן כדורי - את אמיתית</v>
+        <v>עידו כנפי - רגשות מעורבים</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409861&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409880&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אורן כדורי - את אמיתית</v>
+        <v>עידו כנפי - רגשות מעורבים</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אור עמרמי ברוקמן - תמיד חוזר למנגינה</v>
+        <v>מצדה - תמיד שלך קאבר</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409860&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409879&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אור עמרמי ברוקמן - תמיד חוזר למנגינה</v>
+        <v>מצדה - תמיד שלך קאבר</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אדל חן - קומי אורי</v>
+        <v>יהונתן פרץ - תחינתי שמעה יה אל</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409859&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409878&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -811,12 +811,354 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אדל חן - קומי אורי</v>
+        <v>יהונתן פרץ - תחינתי שמעה יה אל</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>טל מוסרי &amp; בתאל צברי - נשימה עושה קסמים</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409877&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>טל מוסרי &amp; בתאל צברי - נשימה עושה קסמים</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>דיג'יי מאוריקו &amp; בצלאל שמיר - מחרוזת פורים 2026</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409876&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>דיג'יי מאוריקו &amp; בצלאל שמיר - מחרוזת פורים 2026</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>דני נגוסו - תקופה כזאת</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409875&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>דני נגוסו - תקופה כזאת</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>דולב הרץ - שלם</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409874&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>דולב הרץ - שלם</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>ברק מזרחי - כמו סם שממכר</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409873&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>ברק מזרחי - כמו סם שממכר</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>אלון מיכאל - מחרוזת נשמה 2026</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409872&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>אלון מיכאל - מחרוזת נשמה 2026</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>אדרת - היו לילות</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="C18" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409871&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>אדרת - היו לילות</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>אביגיל - לגדול</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="C19" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409870&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v>אביגיל - לגדול</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>אבי חיימי - חיכיתי לך</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="C20" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409869&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
+      </c>
+      <c r="D20" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v>אבי חיימי - חיכיתי לך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L20"/>
   </ignoredErrors>
 </worksheet>
 </file>